--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A5C7EED-F651-4E3D-9ECD-EAAD673A3A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1940A826-1C57-4169-A74E-A2CD21457762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25500" yWindow="0" windowWidth="13005" windowHeight="20985" xr2:uid="{0C668139-F74A-4C1F-8FC5-D6FE22A2AFCC}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="28800" windowHeight="15345" xr2:uid="{0C668139-F74A-4C1F-8FC5-D6FE22A2AFCC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
